--- a/verification/cases/roundtrip/picture/init.xlsx
+++ b/verification/cases/roundtrip/picture/init.xlsx
@@ -1,60 +1,64 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <workbookPr defaultThemeVersion="202300"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\frl\AppData\Local\Temp\xlsx-export-inits-3946636136\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{C21DC95A-C4D7-4B21-AAC5-4E95091F09C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView activeTab="0"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="Monozipmx003Ammx002Fmmx002Fmlocalhostmx002Fmcontent.xmlElementm0m0m3m1m0m"/>
-    <sheet name="Sheet2" sheetId="2" r:id="Monozipmx003Ammx002Fmmx002Fmlocalhostmx002Fmcontent.xmlElementm1m0m3m1m0m"/>
-    <sheet name="Sheet3" sheetId="3" r:id="Monozipmx003Ammx002Fmmx002Fmlocalhostmx002Fmcontent.xmlElementm2m0m3m1m0m"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
+    <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
   </sheets>
-  <definedNames/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
   <si>
-    <t xml:space="preserve">Lorem</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ipsum</t>
-  </si>
-  <si>
-    <t xml:space="preserve">dolor</t>
-  </si>
-  <si>
-    <t xml:space="preserve">sit</t>
-  </si>
-  <si>
-    <t xml:space="preserve">amet</t>
-  </si>
-  <si>
-    <t xml:space="preserve">consectetuer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">adipiscing</t>
-  </si>
-  <si>
-    <t xml:space="preserve">elit</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nunc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">at</t>
+    <t>Lorem</t>
+  </si>
+  <si>
+    <t>ipsum</t>
+  </si>
+  <si>
+    <t>dolor</t>
+  </si>
+  <si>
+    <t>sit</t>
+  </si>
+  <si>
+    <t>amet</t>
+  </si>
+  <si>
+    <t>consectetuer</t>
+  </si>
+  <si>
+    <t>adipiscing</t>
+  </si>
+  <si>
+    <t>elit</t>
+  </si>
+  <si>
+    <t>Nunc</t>
+  </si>
+  <si>
+    <t>at</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
-    <numFmt numFmtId="1" formatCode="0.##"/>
-    <numFmt numFmtId="3" formatCode="[$$-409]#,##0.00;[$$-409][Red]-#,##0.00"/>
-  </numFmts>
-  <fonts count="8">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="14" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -73,7 +77,7 @@
       <name val="Arial"/>
     </font>
     <font>
-      <u val="single"/>
+      <u/>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
@@ -98,7 +102,6 @@
       <color rgb="FF000000"/>
       <name val="Calibri"/>
     </font>
-    <font/>
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -107,28 +110,36 @@
     <font>
       <b/>
       <i/>
-      <u val="single"/>
+      <u/>
+      <sz val="11"/>
+      <name val="Calibri"/>
     </font>
     <font>
       <b/>
       <i/>
-      <u val="single"/>
+      <u/>
+      <sz val="11"/>
+      <name val="Calibri"/>
     </font>
     <font>
       <b/>
       <i/>
       <sz val="16"/>
+      <name val="Calibri"/>
     </font>
     <font>
       <b/>
       <i/>
       <sz val="16"/>
-    </font>
-    <font>
-      <color rgb="FF9c0006"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="Calibri"/>
     </font>
   </fonts>
-  <fills>
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -136,71 +147,13 @@
       <patternFill patternType="gray125"/>
     </fill>
     <fill>
-      <patternFill patternType="none"/>
-    </fill>
-    <fill>
-      <patternFill patternType="none"/>
-    </fill>
-    <fill>
-      <patternFill patternType="none"/>
-    </fill>
-    $-$
-    <fill>
-      <patternFill patternType="none"/>
-    </fill>
-    <fill>
-      <patternFill patternType="none"/>
-    </fill>
-    <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFffc7ce"/>
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -211,69 +164,55 @@
   </borders>
   <cellStyleXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fillId="0" borderId="0" applyFont="1" ZMIENNA_contentFontsCount="7" ZMIENNA_styleFontsCount="5" fontId="9"/>
-    <xf numFmtId="0" fillId="0" borderId="0" applyFont="1" ZMIENNA_contentFontsCount="7" ZMIENNA_styleFontsCount="5" fontId="10"/>
-    <xf numFmtId="0" fillId="0" borderId="0" applyFont="1" ZMIENNA_contentFontsCount="7" ZMIENNA_styleFontsCount="5" fontId="11"/>
-    <xf numFmtId="0" fillId="0" borderId="0" applyFont="1" ZMIENNA_contentFontsCount="7" ZMIENNA_styleFontsCount="5" fontId="12" applyAlignment="1">
-      <alignment horizontal="center" vertical="bottom"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fillId="0" borderId="0" applyFont="1" ZMIENNA_contentFontsCount="7" ZMIENNA_styleFontsCount="5" fontId="13" applyAlignment="1">
-      <alignment horizontal="center" vertical="bottom" textRotation="90"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0">
+      <alignment horizontal="center" textRotation="90"/>
     </xf>
-    <xf numFmtId="0" fillId="7" borderId="0" applyFont="1" ZMIENNA_contentFontsCount="7" ZMIENNA_styleFontsCount="5" fontId="14" applyFill="1"/>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fillId="0" borderId="0" xfId="1" applyFont="1" ZMIENNA_contentFontsCount="7" ZMIENNA_styleFontsCount="5" fontId="1"/>
-    <xf numFmtId="0" fillId="0" borderId="0" xfId="1" applyFont="1" ZMIENNA_contentFontsCount="7" ZMIENNA_styleFontsCount="5" fontId="2"/>
-    <xf numFmtId="0" fillId="0" borderId="0" xfId="1" applyFont="1" ZMIENNA_contentFontsCount="7" ZMIENNA_styleFontsCount="5" fontId="3"/>
-    <xf numFmtId="0" fillId="0" borderId="0" xfId="1" applyFont="1" ZMIENNA_contentFontsCount="7" ZMIENNA_styleFontsCount="5" fontId="4" applyAlignment="1">
-      <alignment horizontal="center" vertical="bottom"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fillId="0" borderId="0" xfId="1" applyFont="1" ZMIENNA_contentFontsCount="7" ZMIENNA_styleFontsCount="5" fontId="5" applyAlignment="1">
-      <alignment horizontal="right" vertical="bottom"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fillId="0" borderId="0" xfId="1" applyFont="1" ZMIENNA_contentFontsCount="7" ZMIENNA_styleFontsCount="5" fontId="6"/>
-    <xf numFmtId="0" fillId="0" borderId="0" xfId="1" applyFont="1" ZMIENNA_contentFontsCount="7" ZMIENNA_styleFontsCount="5" fontId="7"/>
-    <xf numFmtId="0" fillId="0" borderId="0" xfId="1" applyFont="1" ZMIENNA_contentFontsCount="7" ZMIENNA_styleFontsCount="5" fontId="9"/>
-    <xf numFmtId="0" fillId="0" borderId="0" xfId="2" applyFont="1" ZMIENNA_contentFontsCount="7" ZMIENNA_styleFontsCount="5" fontId="10"/>
-    <xf numFmtId="0" fillId="0" borderId="0" xfId="3" applyFont="1" ZMIENNA_contentFontsCount="7" ZMIENNA_styleFontsCount="5" fontId="11"/>
-    <xf numFmtId="0" fillId="0" borderId="0" xfId="4" applyFont="1" ZMIENNA_contentFontsCount="7" ZMIENNA_styleFontsCount="5" fontId="12" applyAlignment="1">
-      <alignment horizontal="center" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fillId="0" borderId="0" xfId="5" applyFont="1" ZMIENNA_contentFontsCount="7" ZMIENNA_styleFontsCount="5" fontId="13" applyAlignment="1">
-      <alignment horizontal="center" vertical="bottom" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fillId="7" borderId="0" xfId="6" applyFont="1" ZMIENNA_contentFontsCount="7" ZMIENNA_styleFontsCount="5" fontId="14" applyFill="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="1" applyFont="1"/>
   </cellXfs>
-  <cellStyles>
-    <cellStyle xfId="1" name="Default"/>
-    <cellStyle xfId="2" name="Result"/>
-    <cellStyle xfId="3" name="Result2"/>
-    <cellStyle xfId="4" name="Heading"/>
-    <cellStyle xfId="5" name="Heading1"/>
-    <cellStyle xfId="6" name="Monozipmx003Ammx002Fmmx002Fmlocalhostmx002Fmxlmx002Fmstyles.xmlElementm1m15m1m0m"/>
+  <cellStyles count="7">
+    <cellStyle name="Default" xfId="1" xr:uid="{00000000-0005-0000-0000-000000000000}"/>
+    <cellStyle name="Heading" xfId="4" xr:uid="{00000000-0005-0000-0000-000003000000}"/>
+    <cellStyle name="Heading1" xfId="5" xr:uid="{00000000-0005-0000-0000-000004000000}"/>
+    <cellStyle name="Monozipmx003Ammx002Fmmx002Fmlocalhostmx002Fmxlmx002Fmstyles.xmlElementm1m15m1m0m" xfId="6" xr:uid="{00000000-0005-0000-0000-000005000000}"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Result" xfId="2" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
+    <cellStyle name="Result2" xfId="3" xr:uid="{00000000-0005-0000-0000-000002000000}"/>
   </cellStyles>
-  <dxfs xmlns:config="urn:oasis:names:tc:opendocument:xmlns:config:1.0" xmlns:fo="urn:oasis:names:tc:opendocument:xmlns:xsl-fo-compatible:1.0" count="3">
-    <dxf>
-      <font>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-  </dxfs>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:fo="urn:oasis:names:tc:opendocument:xmlns:xsl-fo-compatible:1.0" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>2</xdr:col>
@@ -289,24 +228,33 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="1" name="Graphics 1" descr="Graphics 1"/>
+        <xdr:cNvPr id="2" name="Graphics 1" descr="Graphics 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvPicPr>
-          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="0"/>
+          <a:picLocks/>
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" r:embed="Monozipmx003Ammx002Fmmx002Fmlocalhostmx002Fmcontent.xmlElementm0m2m3m0m0m3m1m0m"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
           <a:fillRect/>
         </a:stretch>
       </xdr:blipFill>
       <xdr:spPr>
-        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="0" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
           <a:avLst/>
         </a:prstGeom>
-        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:noFill/>
+        <a:ln>
           <a:noFill/>
         </a:ln>
       </xdr:spPr>
@@ -316,121 +264,439 @@
 </xdr:wsDr>
 </file>
 
+<file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+  <a:themeElements>
+    <a:clrScheme name="Office">
+      <a:dk1>
+        <a:sysClr val="windowText" lastClr="000000"/>
+      </a:dk1>
+      <a:lt1>
+        <a:sysClr val="window" lastClr="FFFFFF"/>
+      </a:lt1>
+      <a:dk2>
+        <a:srgbClr val="0E2841"/>
+      </a:dk2>
+      <a:lt2>
+        <a:srgbClr val="E8E8E8"/>
+      </a:lt2>
+      <a:accent1>
+        <a:srgbClr val="156082"/>
+      </a:accent1>
+      <a:accent2>
+        <a:srgbClr val="E97132"/>
+      </a:accent2>
+      <a:accent3>
+        <a:srgbClr val="196B24"/>
+      </a:accent3>
+      <a:accent4>
+        <a:srgbClr val="0F9ED5"/>
+      </a:accent4>
+      <a:accent5>
+        <a:srgbClr val="A02B93"/>
+      </a:accent5>
+      <a:accent6>
+        <a:srgbClr val="4EA72E"/>
+      </a:accent6>
+      <a:hlink>
+        <a:srgbClr val="467886"/>
+      </a:hlink>
+      <a:folHlink>
+        <a:srgbClr val="96607D"/>
+      </a:folHlink>
+    </a:clrScheme>
+    <a:fontScheme name="Office">
+      <a:majorFont>
+        <a:latin typeface="Aptos Display" panose="02110004020202020204"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="游ゴシック Light"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="等线 Light"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Times New Roman"/>
+        <a:font script="Hebr" typeface="Times New Roman"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="MoolBoran"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Times New Roman"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
+      </a:majorFont>
+      <a:minorFont>
+        <a:latin typeface="Aptos Narrow" panose="02110004020202020204"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="游ゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="等线"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Arial"/>
+        <a:font script="Hebr" typeface="Arial"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="DaunPenh"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Arial"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
+      </a:minorFont>
+    </a:fontScheme>
+    <a:fmtScheme name="Office">
+      <a:fillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="110000"/>
+                <a:satMod val="105000"/>
+                <a:tint val="67000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="50000">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="105000"/>
+                <a:satMod val="103000"/>
+                <a:tint val="73000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="105000"/>
+                <a:satMod val="109000"/>
+                <a:tint val="81000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="5400000" scaled="0"/>
+        </a:gradFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:satMod val="103000"/>
+                <a:lumMod val="102000"/>
+                <a:tint val="94000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="50000">
+              <a:schemeClr val="phClr">
+                <a:satMod val="110000"/>
+                <a:lumMod val="100000"/>
+                <a:shade val="100000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="99000"/>
+                <a:satMod val="120000"/>
+                <a:shade val="78000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="5400000" scaled="0"/>
+        </a:gradFill>
+      </a:fillStyleLst>
+      <a:lnStyleLst>
+        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+      </a:lnStyleLst>
+      <a:effectStyleLst>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="63000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+        </a:effectStyle>
+      </a:effectStyleLst>
+      <a:bgFillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr">
+            <a:tint val="95000"/>
+            <a:satMod val="170000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="93000"/>
+                <a:satMod val="150000"/>
+                <a:shade val="98000"/>
+                <a:lumMod val="102000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="50000">
+              <a:schemeClr val="phClr">
+                <a:tint val="98000"/>
+                <a:satMod val="130000"/>
+                <a:shade val="90000"/>
+                <a:lumMod val="103000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="63000"/>
+                <a:satMod val="120000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="5400000" scaled="0"/>
+        </a:gradFill>
+      </a:bgFillStyleLst>
+    </a:fmtScheme>
+  </a:themeElements>
+  <a:objectDefaults>
+    <a:lnDef>
+      <a:spPr/>
+      <a:bodyPr/>
+      <a:lstStyle/>
+      <a:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </a:style>
+    </a:lnDef>
+  </a:objectDefaults>
+  <a:extraClrSchemeLst/>
+  <a:extLst>
+    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
+    </a:ext>
+  </a:extLst>
+</a:theme>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetFormatPr defaultColWidth="11.4666666666667" defaultRowHeight="14" customHeight="true"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:B10"/>
+  <sheetFormatPr defaultColWidth="11.44140625" defaultRowHeight="13.95" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="12.6666666666667" customWidth="1"/>
-    <col min="2" max="3" width="11.4666666666667" customWidth="1"/>
+    <col min="1" max="1" width="12.6640625" customWidth="1"/>
+    <col min="2" max="3" width="11.44140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15" customHeight="1">
+    <row r="1" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="7" t="n">
+      <c r="B1" s="7">
         <v>111</v>
       </c>
     </row>
-    <row r="2" ht="15" customHeight="1">
+    <row r="2" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="7" t="n">
+      <c r="B2" s="7">
         <v>222</v>
       </c>
     </row>
-    <row r="3" ht="15" customHeight="1">
+    <row r="3" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="7" t="n">
+      <c r="B3" s="7">
         <v>333</v>
       </c>
     </row>
-    <row r="4" ht="15" customHeight="1">
+    <row r="4" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="7" t="n">
+      <c r="B4" s="7">
         <v>444</v>
       </c>
     </row>
-    <row r="5" ht="15" customHeight="1">
+    <row r="5" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="7" t="n">
+      <c r="B5" s="7">
         <v>555</v>
       </c>
     </row>
-    <row r="6" ht="15" customHeight="1">
+    <row r="6" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="B6" s="7" t="n">
+      <c r="B6" s="7">
         <v>666</v>
       </c>
     </row>
-    <row r="7" ht="15" customHeight="1">
+    <row r="7" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="B7" s="7" t="n">
+      <c r="B7" s="7">
         <v>777</v>
       </c>
     </row>
-    <row r="8" ht="15" customHeight="1">
+    <row r="8" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="B8" s="7" t="n">
+      <c r="B8" s="7">
         <v>888</v>
       </c>
     </row>
-    <row r="9" ht="15" customHeight="1">
+    <row r="9" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="B9" s="7" t="n">
+      <c r="B9" s="7">
         <v>999</v>
       </c>
     </row>
-    <row r="10" ht="15" customHeight="1">
+    <row r="10" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B10" s="7" t="n">
+      <c r="B10" s="7">
         <v>4995</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.315277777777778" bottom="0.315277777777778" header="0.31496062992125984" footer="0.31496062992125984"/>
+  <pageMargins left="0.7" right="0.7" top="0.31527777777777799" bottom="0.31527777777777799" header="0.31496062992125984" footer="0.31496062992125984"/>
   <pageSetup paperSize="9" orientation="portrait"/>
-  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="d_rId1"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetFormatPr defaultColWidth="11.4666666666667" defaultRowHeight="15" customHeight="true"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+  <dimension ref="A1:IV1"/>
+  <sheetFormatPr defaultColWidth="11.44140625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="256" width="8.4" customWidth="1" style="7"/>
+    <col min="1" max="256" width="8.44140625" style="7" customWidth="1"/>
   </cols>
   <sheetData/>
-  <pageMargins left="0.7" right="0.7" top="0.315277777777778" bottom="0.315277777777778" header="0.31496062992125984" footer="0.31496062992125984"/>
+  <pageMargins left="0.7" right="0.7" top="0.31527777777777799" bottom="0.31527777777777799" header="0.31496062992125984" footer="0.31496062992125984"/>
   <pageSetup paperSize="9" orientation="portrait"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetFormatPr defaultColWidth="11.4666666666667" defaultRowHeight="15" customHeight="true"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+  <dimension ref="A1:IV1"/>
+  <sheetFormatPr defaultColWidth="11.44140625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="256" width="8.4" customWidth="1" style="7"/>
+    <col min="1" max="256" width="8.44140625" style="7" customWidth="1"/>
   </cols>
   <sheetData/>
-  <pageMargins left="0.7" right="0.7" top="0.315277777777778" bottom="0.315277777777778" header="0.31496062992125984" footer="0.31496062992125984"/>
+  <pageMargins left="0.7" right="0.7" top="0.31527777777777799" bottom="0.31527777777777799" header="0.31496062992125984" footer="0.31496062992125984"/>
   <pageSetup paperSize="9" orientation="portrait"/>
 </worksheet>
 </file>